--- a/excel/analysis.xlsx
+++ b/excel/analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analysis-set-c-9697\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36754F1E-FBD4-4BB1-9AD2-159323F6D14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4C71E4-03F5-480A-A89B-B55A625ACA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{B48F3378-1F63-4DDB-978B-C970769D6A82}"/>
   </bookViews>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="30">
   <si>
     <t>assessment_id</t>
   </si>
@@ -149,26 +149,41 @@
     <t>Python</t>
   </si>
   <si>
-    <t>before</t>
-  </si>
-  <si>
-    <t>after</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>pass_flag</t>
+  </si>
+  <si>
+    <t>before duplication removal</t>
+  </si>
+  <si>
+    <t>after duplication removal</t>
+  </si>
+  <si>
+    <t>Batch</t>
+  </si>
+  <si>
+    <t>Pass_flag</t>
+  </si>
+  <si>
+    <t>Moarning</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -206,10 +221,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -958,16 +975,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABF5F244-12A7-402E-9A90-75C6A7780949}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -986,8 +1005,18 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1">
+        <f>COUNTA(assessments[assessment_id])</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1006,8 +1035,19 @@
       <c r="F2" s="2">
         <v>90</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G2" s="4">
+        <f>IF(E2&gt;=50,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2">
+        <f>J1-1</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1026,15 +1066,12 @@
       <c r="F3" s="2">
         <v>70</v>
       </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3">
-        <f>COUNTA(assessments[assessment_id])</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G3" s="4">
+        <f t="shared" ref="G3:G13" si="0">IF(E3&gt;=50,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1053,15 +1090,12 @@
       <c r="F4" s="2">
         <v>85</v>
       </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4">
-        <f>I3-1</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1080,11 +1114,18 @@
       <c r="F5" s="2">
         <v>60</v>
       </c>
-      <c r="I5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1103,8 +1144,18 @@
       <c r="F6" s="2">
         <v>95</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1123,8 +1174,18 @@
       <c r="F7" s="2">
         <v>80</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G7" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1143,8 +1204,18 @@
       <c r="F8" s="2">
         <v>75</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G8" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1163,8 +1234,12 @@
       <c r="F9" s="2">
         <v>88</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G9" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1183,8 +1258,12 @@
       <c r="F10" s="2">
         <v>98</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G10" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1203,8 +1282,12 @@
       <c r="F11" s="2">
         <v>82</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G11" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1223,8 +1306,12 @@
       <c r="F12" s="2">
         <v>92</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G12" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1242,6 +1329,10 @@
       </c>
       <c r="F13" s="2">
         <v>65</v>
+      </c>
+      <c r="G13" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -1325,6 +1416,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/excel/analysis.xlsx
+++ b/excel/analysis.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analysis-set-c-9697\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4C71E4-03F5-480A-A89B-B55A625ACA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A6662B-0465-4133-9FD7-1BDE02EE8803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{B48F3378-1F63-4DDB-978B-C970769D6A82}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{B48F3378-1F63-4DDB-978B-C970769D6A82}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw" sheetId="5" r:id="rId1"/>
@@ -22,6 +22,9 @@
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">Raw!$A$1:$F$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="23" r:id="rId5"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -75,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="35">
   <si>
     <t>assessment_id</t>
   </si>
@@ -165,6 +168,21 @@
   </si>
   <si>
     <t>Moarning</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>Average of score</t>
   </si>
 </sst>
 </file>
@@ -221,12 +239,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -252,6 +274,1493 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[analysis.xlsx]Summary!PivotTable6</c:name>
+    <c:fmtId val="13"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="1"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$B$1:$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$A$3:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Business</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Technology</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$B$3:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>58.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CCFA-46CE-9BF1-25C74B154EF2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$C$1:$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Feb</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$A$3:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Business</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Technology</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$C$3:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>67.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>58</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CCFA-46CE-9BF1-25C74B154EF2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$D$1:$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mar</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$A$3:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Business</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Technology</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$D$3:$D$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>58.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-CCFA-46CE-9BF1-25C74B154EF2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:shape val="box"/>
+        <c:axId val="1081612304"/>
+        <c:axId val="1076926192"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="1081612304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1076926192"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1076926192"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1081612304"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D354E6BD-7D29-64D1-5761-962606AC8670}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OM" refreshedDate="46298.440799652781" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{6C6157B9-A56F-45DA-AC8D-4A48EAD0084B}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:H13" sheet="Clean"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="assessment_id" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="12"/>
+    </cacheField>
+    <cacheField name="month" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Jan"/>
+        <s v="Feb"/>
+        <s v="Mar"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="course_id" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="batch" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="score" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="38" maxValue="90"/>
+    </cacheField>
+    <cacheField name="attendance_pct" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="60" maxValue="98"/>
+    </cacheField>
+    <cacheField name="pass_flag" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Department" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Business"/>
+        <s v="Technology"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <s v="C1"/>
+    <s v="Morning"/>
+    <n v="72"/>
+    <n v="90"/>
+    <n v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="0"/>
+    <s v="C2"/>
+    <s v="Evening"/>
+    <n v="45"/>
+    <n v="70"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="0"/>
+    <s v="C3"/>
+    <s v="Morning"/>
+    <n v="65"/>
+    <n v="85"/>
+    <n v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="0"/>
+    <s v="C4"/>
+    <s v="Weekend"/>
+    <n v="38"/>
+    <n v="60"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="1"/>
+    <s v="C1"/>
+    <s v="Evening"/>
+    <n v="80"/>
+    <n v="95"/>
+    <n v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="1"/>
+    <s v="C2"/>
+    <s v="Weekend"/>
+    <n v="55"/>
+    <n v="80"/>
+    <n v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="1"/>
+    <s v="C3"/>
+    <s v="Morning"/>
+    <n v="48"/>
+    <n v="75"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="1"/>
+    <s v="C4"/>
+    <s v="Evening"/>
+    <n v="68"/>
+    <n v="88"/>
+    <n v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="2"/>
+    <s v="C1"/>
+    <s v="Weekend"/>
+    <n v="90"/>
+    <n v="98"/>
+    <n v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="2"/>
+    <s v="C2"/>
+    <s v="Morning"/>
+    <n v="60"/>
+    <n v="82"/>
+    <n v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <x v="2"/>
+    <s v="C3"/>
+    <s v="Evening"/>
+    <n v="75"/>
+    <n v="92"/>
+    <n v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <x v="2"/>
+    <s v="C4"/>
+    <s v="Weekend"/>
+    <n v="42"/>
+    <n v="65"/>
+    <n v="0"/>
+    <x v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{71929256-CAA9-4A3E-B7C3-9EAC44030825}" name="PivotTable6" cacheId="23" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+  <location ref="A1:E5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of score" fld="4" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="13" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="13" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -975,7 +2484,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABF5F244-12A7-402E-9A90-75C6A7780949}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
@@ -983,10 +2492,11 @@
     <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1008,15 +2518,18 @@
       <c r="G1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
         <v>25</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <f>COUNTA(assessments[assessment_id])</f>
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1039,15 +2552,19 @@
         <f>IF(E2&gt;=50,1,0)</f>
         <v>1</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H2" s="2" t="str" cm="1">
+        <f t="array" ref="H2">_xlfn.IFS(C2="C1","Business", C2="C2","Business", C2="C3","Technology", C2="C4","Technology", TRUE,"Null")</f>
+        <v>Business</v>
+      </c>
+      <c r="J2" t="s">
         <v>26</v>
       </c>
-      <c r="J2">
-        <f>J1-1</f>
+      <c r="K2">
+        <f>K1-1</f>
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1070,8 +2587,12 @@
         <f t="shared" ref="G3:G13" si="0">IF(E3&gt;=50,1,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H3" s="2" t="str" cm="1">
+        <f t="array" ref="H3">_xlfn.IFS(C3="C1","Business", C3="C2","Business", C3="C3","Technology", C3="C4","Technology", TRUE,"Null")</f>
+        <v>Business</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1094,8 +2615,12 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H4" s="2" t="str" cm="1">
+        <f t="array" ref="H4">_xlfn.IFS(C4="C1","Business", C4="C2","Business", C4="C3","Technology", C4="C4","Technology", TRUE,"Null")</f>
+        <v>Technology</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1118,14 +2643,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="H5" s="2" t="str" cm="1">
+        <f t="array" ref="H5">_xlfn.IFS(C5="C1","Business", C5="C2","Business", C5="C3","Technology", C5="C4","Technology", TRUE,"Null")</f>
+        <v>Technology</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1148,14 +2677,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="H6" s="2" t="str" cm="1">
+        <f t="array" ref="H6">_xlfn.IFS(C6="C1","Business", C6="C2","Business", C6="C3","Technology", C6="C4","Technology", TRUE,"Null")</f>
+        <v>Business</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1178,14 +2711,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="H7" s="2" t="str" cm="1">
+        <f t="array" ref="H7">_xlfn.IFS(C7="C1","Business", C7="C2","Business", C7="C3","Technology", C7="C4","Technology", TRUE,"Null")</f>
+        <v>Business</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1208,14 +2745,18 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="H8" s="2" t="str" cm="1">
+        <f t="array" ref="H8">_xlfn.IFS(C8="C1","Business", C8="C2","Business", C8="C3","Technology", C8="C4","Technology", TRUE,"Null")</f>
+        <v>Technology</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1238,8 +2779,12 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H9" s="2" t="str" cm="1">
+        <f t="array" ref="H9">_xlfn.IFS(C9="C1","Business", C9="C2","Business", C9="C3","Technology", C9="C4","Technology", TRUE,"Null")</f>
+        <v>Technology</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1262,8 +2807,12 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H10" s="2" t="str" cm="1">
+        <f t="array" ref="H10">_xlfn.IFS(C10="C1","Business", C10="C2","Business", C10="C3","Technology", C10="C4","Technology", TRUE,"Null")</f>
+        <v>Business</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1286,8 +2835,12 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H11" s="2" t="str" cm="1">
+        <f t="array" ref="H11">_xlfn.IFS(C11="C1","Business", C11="C2","Business", C11="C3","Technology", C11="C4","Technology", TRUE,"Null")</f>
+        <v>Business</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1310,8 +2863,12 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H12" s="2" t="str" cm="1">
+        <f t="array" ref="H12">_xlfn.IFS(C12="C1","Business", C12="C2","Business", C12="C3","Technology", C12="C4","Technology", TRUE,"Null")</f>
+        <v>Technology</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1334,8 +2891,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H13" s="2" t="str" cm="1">
+        <f t="array" ref="H13">_xlfn.IFS(C13="C1","Business", C13="C2","Business", C13="C3","Technology", C13="C4","Technology", TRUE,"Null")</f>
+        <v>Technology</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>2</v>
       </c>
@@ -1345,17 +2906,17 @@
       <c r="C17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="L17" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -1365,18 +2926,18 @@
       <c r="C18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="2" t="str" cm="1">
-        <f t="array" ref="G18:H18">_xlfn.XLOOKUP(F18,A18:A21,B18:C21)</f>
+      <c r="K18" s="2" t="str" cm="1">
+        <f t="array" ref="K18:L18">_xlfn.XLOOKUP(J18,A18:A21,B18:C21)</f>
         <v>Python</v>
       </c>
-      <c r="H18" s="2" t="str">
+      <c r="L18" s="2" t="str">
         <v>Technology</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -1387,7 +2948,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
@@ -1398,7 +2959,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
@@ -1411,7 +2972,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18" xr:uid="{D9BF7F1E-7451-4120-AEB0-EA8847E7C8EA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J18" xr:uid="{D9BF7F1E-7451-4120-AEB0-EA8847E7C8EA}">
       <formula1>$A$18:$A$21</formula1>
     </dataValidation>
   </dataValidations>
@@ -1422,10 +2983,94 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F8062F-FBD5-4F17-A450-49D043434F42}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="1">
+        <v>58.5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>67.5</v>
+      </c>
+      <c r="D3" s="1">
+        <v>75</v>
+      </c>
+      <c r="E3" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1">
+        <v>51.5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>58</v>
+      </c>
+      <c r="D4" s="1">
+        <v>58.5</v>
+      </c>
+      <c r="E4" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="1">
+        <v>55</v>
+      </c>
+      <c r="C5" s="1">
+        <v>62.75</v>
+      </c>
+      <c r="D5" s="1">
+        <v>66.75</v>
+      </c>
+      <c r="E5" s="1">
+        <v>61.5</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
